--- a/docs/plc_modbus_寄存器地址表_v0.1.xlsx
+++ b/docs/plc_modbus_寄存器地址表_v0.1.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\兰铀\封头检测工位\文档\通信协议\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EF1F23-66CE-4711-AB1D-0D86CCECB482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="plc_modbus_地址表_初稿_v0.1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -823,20 +830,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -845,13 +850,11 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -859,7 +862,6 @@
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -867,7 +869,6 @@
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -875,11 +876,161 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -889,35 +1040,227 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5597"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -940,9 +1283,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -951,48 +1536,92 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1041,7 +1670,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1074,26 +1703,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1126,23 +1738,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1284,31 +1879,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H106"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="1" customWidth="1"/>
-    <col min="4" max="4" width="31.4140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.9140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.4140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.4166666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.9166666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.4166666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="38.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="71.4140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="71.4166666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="16.5" customHeight="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1334,7 +1924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="28" customHeight="1" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1360,7 +1950,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="28" customHeight="1" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1386,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="28" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1412,7 +2002,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="28" customHeight="1" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1438,7 +2028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" ht="28" customHeight="1" spans="1:8">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -1464,7 +2054,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" ht="28" customHeight="1" spans="1:8">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -1490,7 +2080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" ht="28" customHeight="1" spans="1:8">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -1516,7 +2106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" ht="28" customHeight="1" spans="1:8">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1542,7 +2132,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" ht="28" customHeight="1" spans="1:8">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -1568,7 +2158,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" ht="28" customHeight="1" spans="1:8">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1594,7 +2184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" ht="28" customHeight="1" spans="1:8">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1620,7 +2210,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" ht="28" customHeight="1" spans="1:8">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
@@ -1646,7 +2236,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" ht="28" customHeight="1" spans="1:8">
       <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1672,7 +2262,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" ht="28" customHeight="1" spans="1:8">
       <c r="A15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1698,7 +2288,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" ht="28" customHeight="1" spans="1:8">
       <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
@@ -1724,7 +2314,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" ht="28" customHeight="1" spans="1:8">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +2340,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" ht="28" customHeight="1" spans="1:8">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1776,7 +2366,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" ht="28" customHeight="1" spans="1:8">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
@@ -1802,7 +2392,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" ht="28" customHeight="1" spans="1:8">
       <c r="A20" s="7" t="s">
         <v>8</v>
       </c>
@@ -1828,7 +2418,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" ht="28" customHeight="1" spans="1:8">
       <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1854,7 +2444,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" ht="28" customHeight="1" spans="1:8">
       <c r="A22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1880,7 +2470,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" ht="28" customHeight="1" spans="1:8">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1906,7 +2496,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" ht="28" customHeight="1" spans="1:8">
       <c r="A24" s="3" t="s">
         <v>8</v>
       </c>
@@ -1932,7 +2522,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" ht="28" customHeight="1" spans="1:8">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -1958,7 +2548,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" ht="28" customHeight="1" spans="1:8">
       <c r="A26" s="3" t="s">
         <v>8</v>
       </c>
@@ -1984,7 +2574,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" ht="28" customHeight="1" spans="1:8">
       <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2010,7 +2600,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" ht="28" customHeight="1" spans="1:8">
       <c r="A28" s="3" t="s">
         <v>8</v>
       </c>
@@ -2036,7 +2626,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" ht="28" customHeight="1" spans="1:8">
       <c r="A29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2062,7 +2652,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" ht="28" customHeight="1" spans="1:8">
       <c r="A30" s="7" t="s">
         <v>8</v>
       </c>
@@ -2088,7 +2678,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" ht="28" customHeight="1" spans="1:8">
       <c r="A31" s="7" t="s">
         <v>8</v>
       </c>
@@ -2114,7 +2704,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" ht="28" customHeight="1" spans="1:8">
       <c r="A32" s="7" t="s">
         <v>8</v>
       </c>
@@ -2140,7 +2730,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" ht="28" customHeight="1" spans="1:8">
       <c r="A33" s="7" t="s">
         <v>8</v>
       </c>
@@ -2166,7 +2756,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" ht="28" customHeight="1" spans="1:8">
       <c r="A34" s="7" t="s">
         <v>8</v>
       </c>
@@ -2192,7 +2782,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" ht="28" customHeight="1" spans="1:8">
       <c r="A35" s="7" t="s">
         <v>8</v>
       </c>
@@ -2218,7 +2808,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" ht="28" customHeight="1" spans="1:8">
       <c r="A36" s="7" t="s">
         <v>8</v>
       </c>
@@ -2244,7 +2834,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" ht="28" customHeight="1" spans="1:8">
       <c r="A37" s="7" t="s">
         <v>8</v>
       </c>
@@ -2270,7 +2860,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" ht="28" customHeight="1" spans="1:8">
       <c r="A38" s="7" t="s">
         <v>8</v>
       </c>
@@ -2296,7 +2886,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" ht="28" customHeight="1" spans="1:8">
       <c r="A39" s="7" t="s">
         <v>8</v>
       </c>
@@ -2322,7 +2912,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" ht="28" customHeight="1" spans="1:8">
       <c r="A40" s="7" t="s">
         <v>8</v>
       </c>
@@ -2348,7 +2938,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" ht="28" customHeight="1" spans="1:8">
       <c r="A41" s="7" t="s">
         <v>8</v>
       </c>
@@ -2374,7 +2964,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" ht="28" customHeight="1" spans="1:8">
       <c r="A42" s="9" t="s">
         <v>96</v>
       </c>
@@ -2400,7 +2990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" ht="28" customHeight="1" spans="1:8">
       <c r="A43" s="9" t="s">
         <v>96</v>
       </c>
@@ -2426,7 +3016,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" ht="28" customHeight="1" spans="1:8">
       <c r="A44" s="9" t="s">
         <v>96</v>
       </c>
@@ -2452,7 +3042,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" ht="28" customHeight="1" spans="1:8">
       <c r="A45" s="5" t="s">
         <v>96</v>
       </c>
@@ -2478,7 +3068,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" ht="28" customHeight="1" spans="1:8">
       <c r="A46" s="5" t="s">
         <v>96</v>
       </c>
@@ -2504,7 +3094,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" ht="28" customHeight="1" spans="1:8">
       <c r="A47" s="9" t="s">
         <v>96</v>
       </c>
@@ -2530,7 +3120,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" ht="28" customHeight="1" spans="1:8">
       <c r="A48" s="9" t="s">
         <v>96</v>
       </c>
@@ -2556,7 +3146,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" ht="28" customHeight="1" spans="1:8">
       <c r="A49" s="9" t="s">
         <v>96</v>
       </c>
@@ -2582,7 +3172,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" ht="28" customHeight="1" spans="1:8">
       <c r="A50" s="9" t="s">
         <v>96</v>
       </c>
@@ -2608,7 +3198,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" ht="28" customHeight="1" spans="1:8">
       <c r="A51" s="9" t="s">
         <v>96</v>
       </c>
@@ -2634,7 +3224,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" ht="28" customHeight="1" spans="1:8">
       <c r="A52" s="9" t="s">
         <v>96</v>
       </c>
@@ -2660,7 +3250,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" ht="28" customHeight="1" spans="1:8">
       <c r="A53" s="9" t="s">
         <v>96</v>
       </c>
@@ -2686,7 +3276,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" ht="28" customHeight="1" spans="1:8">
       <c r="A54" s="9" t="s">
         <v>96</v>
       </c>
@@ -2712,7 +3302,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" ht="28" customHeight="1" spans="1:8">
       <c r="A55" s="9" t="s">
         <v>96</v>
       </c>
@@ -2738,7 +3328,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" ht="28" customHeight="1" spans="1:8">
       <c r="A56" s="9" t="s">
         <v>96</v>
       </c>
@@ -2764,7 +3354,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" ht="28" customHeight="1" spans="1:8">
       <c r="A57" s="9" t="s">
         <v>96</v>
       </c>
@@ -2790,7 +3380,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" ht="28" customHeight="1" spans="1:8">
       <c r="A58" s="9" t="s">
         <v>96</v>
       </c>
@@ -2816,7 +3406,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" ht="28" customHeight="1" spans="1:8">
       <c r="A59" s="9" t="s">
         <v>96</v>
       </c>
@@ -2842,7 +3432,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" ht="28" customHeight="1" spans="1:8">
       <c r="A60" s="9" t="s">
         <v>96</v>
       </c>
@@ -2868,7 +3458,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" ht="28" customHeight="1" spans="1:8">
       <c r="A61" s="9" t="s">
         <v>96</v>
       </c>
@@ -2894,7 +3484,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" ht="28" customHeight="1" spans="1:8">
       <c r="A62" s="9" t="s">
         <v>96</v>
       </c>
@@ -2920,7 +3510,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" ht="28" customHeight="1" spans="1:8">
       <c r="A63" s="9" t="s">
         <v>96</v>
       </c>
@@ -2946,7 +3536,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" ht="28" customHeight="1" spans="1:8">
       <c r="A64" s="9" t="s">
         <v>96</v>
       </c>
@@ -2972,7 +3562,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" ht="28" customHeight="1" spans="1:8">
       <c r="A65" s="9" t="s">
         <v>96</v>
       </c>
@@ -2998,7 +3588,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" ht="28" customHeight="1" spans="1:8">
       <c r="A66" s="9" t="s">
         <v>96</v>
       </c>
@@ -3024,7 +3614,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" ht="28" customHeight="1" spans="1:8">
       <c r="A67" s="9" t="s">
         <v>96</v>
       </c>
@@ -3050,7 +3640,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" ht="28" customHeight="1" spans="1:8">
       <c r="A68" s="9" t="s">
         <v>96</v>
       </c>
@@ -3076,7 +3666,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" ht="28" customHeight="1" spans="1:8">
       <c r="A69" s="9" t="s">
         <v>96</v>
       </c>
@@ -3102,7 +3692,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" ht="28" customHeight="1" spans="1:8">
       <c r="A70" s="9" t="s">
         <v>96</v>
       </c>
@@ -3128,7 +3718,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" ht="28" customHeight="1" spans="1:8">
       <c r="A71" s="9" t="s">
         <v>96</v>
       </c>
@@ -3154,7 +3744,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" ht="28" customHeight="1" spans="1:8">
       <c r="A72" s="9" t="s">
         <v>96</v>
       </c>
@@ -3180,7 +3770,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" ht="28" customHeight="1" spans="1:8">
       <c r="A73" s="9" t="s">
         <v>96</v>
       </c>
@@ -3206,7 +3796,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" ht="28" customHeight="1" spans="1:8">
       <c r="A74" s="9" t="s">
         <v>96</v>
       </c>
@@ -3232,7 +3822,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" ht="28" customHeight="1" spans="1:8">
       <c r="A75" s="9" t="s">
         <v>96</v>
       </c>
@@ -3258,7 +3848,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" ht="28" customHeight="1" spans="1:8">
       <c r="A76" s="9" t="s">
         <v>96</v>
       </c>
@@ -3284,7 +3874,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" ht="28" customHeight="1" spans="1:8">
       <c r="A77" s="9" t="s">
         <v>96</v>
       </c>
@@ -3310,7 +3900,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" ht="28" customHeight="1" spans="1:8">
       <c r="A78" s="9" t="s">
         <v>96</v>
       </c>
@@ -3336,7 +3926,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" ht="28" customHeight="1" spans="1:8">
       <c r="A79" s="9" t="s">
         <v>96</v>
       </c>
@@ -3362,7 +3952,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" ht="28" customHeight="1" spans="1:8">
       <c r="A80" s="9" t="s">
         <v>96</v>
       </c>
@@ -3388,7 +3978,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" ht="28" customHeight="1" spans="1:8">
       <c r="A81" s="9" t="s">
         <v>96</v>
       </c>
@@ -3414,7 +4004,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" ht="28" customHeight="1" spans="1:8">
       <c r="A82" s="9" t="s">
         <v>96</v>
       </c>
@@ -3440,7 +4030,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" ht="28" customHeight="1" spans="1:8">
       <c r="A83" s="9" t="s">
         <v>96</v>
       </c>
@@ -3466,7 +4056,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" ht="28" customHeight="1" spans="1:8">
       <c r="A84" s="9" t="s">
         <v>96</v>
       </c>
@@ -3492,7 +4082,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" ht="28" customHeight="1" spans="1:8">
       <c r="A85" s="9" t="s">
         <v>96</v>
       </c>
@@ -3518,7 +4108,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" ht="28" customHeight="1" spans="1:8">
       <c r="A86" s="9" t="s">
         <v>96</v>
       </c>
@@ -3544,7 +4134,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" ht="28" customHeight="1" spans="1:8">
       <c r="A87" s="9" t="s">
         <v>96</v>
       </c>
@@ -3570,7 +4160,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" ht="28" customHeight="1" spans="1:8">
       <c r="A88" s="9" t="s">
         <v>96</v>
       </c>
@@ -3596,7 +4186,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" ht="28" customHeight="1" spans="1:8">
       <c r="A89" s="9" t="s">
         <v>96</v>
       </c>
@@ -3622,7 +4212,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" ht="28" customHeight="1" spans="1:8">
       <c r="A90" s="5" t="s">
         <v>96</v>
       </c>
@@ -3648,7 +4238,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" ht="28" customHeight="1" spans="1:8">
       <c r="A91" s="5" t="s">
         <v>96</v>
       </c>
@@ -3674,7 +4264,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" ht="28" customHeight="1" spans="1:8">
       <c r="A92" s="9" t="s">
         <v>96</v>
       </c>
@@ -3700,7 +4290,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" ht="28" customHeight="1" spans="1:8">
       <c r="A93" s="9" t="s">
         <v>96</v>
       </c>
@@ -3726,7 +4316,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" ht="28" customHeight="1" spans="1:8">
       <c r="A94" s="9" t="s">
         <v>96</v>
       </c>
@@ -3752,7 +4342,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" ht="28" customHeight="1" spans="1:8">
       <c r="A95" s="5" t="s">
         <v>96</v>
       </c>
@@ -3778,7 +4368,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" ht="28" customHeight="1" spans="1:8">
       <c r="A96" s="7" t="s">
         <v>96</v>
       </c>
@@ -3804,7 +4394,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" ht="28" customHeight="1" spans="1:8">
       <c r="A97" s="7" t="s">
         <v>96</v>
       </c>
@@ -3830,7 +4420,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" ht="28" customHeight="1" spans="1:8">
       <c r="A98" s="7" t="s">
         <v>96</v>
       </c>
@@ -3856,7 +4446,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" ht="28" customHeight="1" spans="1:8">
       <c r="A99" s="7" t="s">
         <v>96</v>
       </c>
@@ -3882,7 +4472,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" ht="28" customHeight="1" spans="1:8">
       <c r="A100" s="7" t="s">
         <v>96</v>
       </c>
@@ -3908,7 +4498,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" ht="28" customHeight="1" spans="1:8">
       <c r="A101" s="7" t="s">
         <v>96</v>
       </c>
@@ -3934,7 +4524,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" ht="28" customHeight="1" spans="1:8">
       <c r="A102" s="7" t="s">
         <v>96</v>
       </c>
@@ -3960,7 +4550,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" ht="28" customHeight="1" spans="1:8">
       <c r="A103" s="7" t="s">
         <v>96</v>
       </c>
@@ -3986,7 +4576,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" ht="28" customHeight="1" spans="1:8">
       <c r="A104" s="7" t="s">
         <v>96</v>
       </c>
@@ -4012,7 +4602,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" ht="28" customHeight="1" spans="1:8">
       <c r="A105" s="7" t="s">
         <v>96</v>
       </c>
@@ -4038,7 +4628,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" ht="28" customHeight="1" spans="1:8">
       <c r="A106" s="7" t="s">
         <v>96</v>
       </c>
@@ -4065,7 +4655,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/plc_modbus_寄存器地址表_v0.1.xlsx
+++ b/docs/plc_modbus_寄存器地址表_v0.1.xlsx
@@ -617,7 +617,7 @@
     <t>最终检测结果</t>
   </si>
   <si>
-    <t>0未判定,1OK,2NG,3复检,6超时,7算法失败</t>
+    <t>0未判定,1OK,2NG,3复检,6超时,7算法失败；；；超时NG，其它全部给ok</t>
   </si>
   <si>
     <t>NG_Reason_Word0</t>
@@ -837,7 +837,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -877,13 +877,6 @@
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1030,7 +1023,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1082,12 +1075,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1386,67 +1373,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1461,73 +1451,70 @@
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/docs/plc_modbus_寄存器地址表_v0.1.xlsx
+++ b/docs/plc_modbus_寄存器地址表_v0.1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="254">
   <si>
     <t>方向</t>
   </si>
@@ -272,111 +272,78 @@
     <t>结果区清理触发</t>
   </si>
   <si>
-    <t>Reserved_CmdExt_29</t>
-  </si>
-  <si>
-    <t>用于后续新增命令、握手或诊断字段</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_30</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_31</t>
-  </si>
-  <si>
-    <t>控制命令扩展预留</t>
-  </si>
-  <si>
-    <t>用于后续新增模式、联锁、诊断或工艺控制命令</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_32</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_33</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_34</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_35</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_36</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_37</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_38</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_39</t>
-  </si>
-  <si>
-    <t>Reserved_CmdExt_40</t>
+    <t>40029~40030</t>
+  </si>
+  <si>
+    <t>RobotTcp_X</t>
+  </si>
+  <si>
+    <t>FLOAT32</t>
+  </si>
+  <si>
+    <t>机械臂末端中心点X坐标</t>
+  </si>
+  <si>
+    <t>单位mm, CDAB字序</t>
+  </si>
+  <si>
+    <t>40031~40032</t>
+  </si>
+  <si>
+    <t>RobotTcp_Y</t>
+  </si>
+  <si>
+    <t>机械臂末端中心点Y坐标</t>
+  </si>
+  <si>
+    <t>40033~40034</t>
+  </si>
+  <si>
+    <t>RobotTcp_Z</t>
+  </si>
+  <si>
+    <t>机械臂末端中心点Z坐标</t>
+  </si>
+  <si>
+    <t>40035~40036</t>
+  </si>
+  <si>
+    <t>RobotTcp_Rx</t>
+  </si>
+  <si>
+    <t>机械臂末端姿态Rx</t>
+  </si>
+  <si>
+    <t>单位deg, CDAB字序</t>
+  </si>
+  <si>
+    <t>40037~40038</t>
+  </si>
+  <si>
+    <t>RobotTcp_Ry</t>
+  </si>
+  <si>
+    <t>机械臂末端姿态Ry</t>
+  </si>
+  <si>
+    <t>40039~40040</t>
+  </si>
+  <si>
+    <t>RobotTcp_Rz</t>
+  </si>
+  <si>
+    <t>机械臂末端姿态Rz</t>
   </si>
   <si>
     <t>IPC-&gt;PLC</t>
   </si>
   <si>
-    <t>IPC_Heartbeat</t>
+    <t>IPC_Ready</t>
   </si>
   <si>
     <t>IPC写/PLC读</t>
   </si>
   <si>
-    <t>IPC心跳</t>
-  </si>
-  <si>
-    <t>IPC_SystemState</t>
-  </si>
-  <si>
-    <t>IPC系统状态</t>
-  </si>
-  <si>
-    <t>0未初始化,1初始化中,2就绪,3忙碌,4暂停,5故障</t>
-  </si>
-  <si>
-    <t>IPC_CurrentStage</t>
-  </si>
-  <si>
-    <t>当前处理阶段</t>
-  </si>
-  <si>
-    <t>按正文定义</t>
-  </si>
-  <si>
-    <t>IPC_AlarmLevel</t>
-  </si>
-  <si>
-    <t>当前报警等级</t>
-  </si>
-  <si>
-    <t>0无,1提示,2黄色预警,3红色预警停机</t>
-  </si>
-  <si>
-    <t>IPC_AlarmCode</t>
-  </si>
-  <si>
-    <t>当前主报警码</t>
-  </si>
-  <si>
-    <t>0表示无报警</t>
-  </si>
-  <si>
-    <t>IPC_WarnCode</t>
-  </si>
-  <si>
-    <t>当前预警码</t>
-  </si>
-  <si>
-    <t>0表示无预警</t>
-  </si>
-  <si>
-    <t>IPC_Ready</t>
-  </si>
-  <si>
     <t>IPC是否可接受新任务</t>
   </si>
   <si>
@@ -468,9 +435,6 @@
   </si>
   <si>
     <t>Load_X</t>
-  </si>
-  <si>
-    <t>FLOAT32</t>
   </si>
   <si>
     <t>抓取点X坐标</t>
@@ -1373,153 +1337,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -2640,2007 +2604,1707 @@
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:8">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="7">
-        <v>40029</v>
-      </c>
-      <c r="C30" s="7">
+      <c r="B30" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="3">
         <v>28</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="7" t="s">
+      <c r="D30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>82</v>
+      <c r="G30" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:8">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="7">
-        <v>40030</v>
-      </c>
-      <c r="C31" s="7">
-        <v>29</v>
-      </c>
-      <c r="D31" s="7" t="s">
+      <c r="B31" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="3">
+        <v>30</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>82</v>
+      <c r="G31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:8">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="7">
-        <v>40031</v>
-      </c>
-      <c r="C32" s="7">
-        <v>30</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="7" t="s">
+      <c r="B32" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="3">
+        <v>32</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:8">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="7">
-        <v>40032</v>
-      </c>
-      <c r="C33" s="7">
-        <v>31</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="7" t="s">
+      <c r="B33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="3">
+        <v>34</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>86</v>
+      <c r="G33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:8">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="7">
-        <v>40033</v>
-      </c>
-      <c r="C34" s="7">
-        <v>32</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="7" t="s">
+      <c r="B34" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" s="3">
+        <v>36</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G34" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>86</v>
+      <c r="G34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:8">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="7">
-        <v>40034</v>
-      </c>
-      <c r="C35" s="7">
-        <v>33</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="7" t="s">
+      <c r="B35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="3">
+        <v>38</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G35" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>86</v>
+      <c r="G35" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:8">
-      <c r="A36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="7">
-        <v>40035</v>
-      </c>
-      <c r="C36" s="7">
-        <v>34</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>86</v>
+      <c r="A36" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="9">
+        <v>40107</v>
+      </c>
+      <c r="C36" s="9">
+        <v>106</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:8">
-      <c r="A37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="7">
-        <v>40036</v>
-      </c>
-      <c r="C37" s="7">
-        <v>35</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>86</v>
+      <c r="A37" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="9">
+        <v>40108</v>
+      </c>
+      <c r="C37" s="9">
+        <v>107</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:8">
-      <c r="A38" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="7">
-        <v>40037</v>
-      </c>
-      <c r="C38" s="7">
-        <v>36</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>86</v>
+      <c r="A38" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="9">
+        <v>40109</v>
+      </c>
+      <c r="C38" s="9">
+        <v>108</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:8">
-      <c r="A39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="7">
-        <v>40038</v>
-      </c>
-      <c r="C39" s="7">
-        <v>37</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>86</v>
+      <c r="A39" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="9">
+        <v>40110</v>
+      </c>
+      <c r="C39" s="9">
+        <v>109</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:8">
-      <c r="A40" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="7">
-        <v>40039</v>
-      </c>
-      <c r="C40" s="7">
-        <v>38</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>86</v>
+      <c r="A40" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40" s="9">
+        <v>40111</v>
+      </c>
+      <c r="C40" s="9">
+        <v>110</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:8">
-      <c r="A41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="7">
-        <v>40040</v>
-      </c>
-      <c r="C41" s="7">
-        <v>39</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>86</v>
+      <c r="A41" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="9">
+        <v>40112</v>
+      </c>
+      <c r="C41" s="9">
+        <v>111</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:8">
       <c r="A42" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B42" s="9">
-        <v>40101</v>
+        <v>40113</v>
       </c>
       <c r="C42" s="9">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:8">
       <c r="A43" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B43" s="9">
-        <v>40102</v>
+        <v>40114</v>
       </c>
       <c r="C43" s="9">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1" spans="1:8">
       <c r="A44" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B44" s="9">
-        <v>40103</v>
+        <v>40115</v>
       </c>
       <c r="C44" s="9">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1" spans="1:8">
-      <c r="A45" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" s="5">
-        <v>40104</v>
-      </c>
-      <c r="C45" s="5">
-        <v>103</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>108</v>
+      <c r="A45" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="9">
+        <v>40116</v>
+      </c>
+      <c r="C45" s="9">
+        <v>115</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1" spans="1:8">
-      <c r="A46" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B46" s="5">
-        <v>40105</v>
-      </c>
-      <c r="C46" s="5">
-        <v>104</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>111</v>
+      <c r="A46" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" s="9">
+        <v>40117</v>
+      </c>
+      <c r="C46" s="9">
+        <v>116</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1" spans="1:8">
       <c r="A47" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B47" s="9">
-        <v>40106</v>
+        <v>102</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>134</v>
       </c>
       <c r="C47" s="9">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1" spans="1:8">
       <c r="A48" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B48" s="9">
-        <v>40107</v>
+        <v>102</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>138</v>
       </c>
       <c r="C48" s="9">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1" spans="1:8">
       <c r="A49" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="9">
-        <v>40108</v>
+        <v>102</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="C49" s="9">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>28</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1" spans="1:8">
       <c r="A50" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B50" s="9">
-        <v>40109</v>
+        <v>102</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="C50" s="9">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:8">
       <c r="A51" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B51" s="9">
-        <v>40110</v>
+        <v>102</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="C51" s="9">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1" spans="1:8">
       <c r="A52" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B52" s="9">
-        <v>40111</v>
+        <v>102</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>151</v>
       </c>
       <c r="C52" s="9">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1" spans="1:8">
       <c r="A53" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B53" s="9">
-        <v>40112</v>
+        <v>40130</v>
       </c>
       <c r="C53" s="9">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1" spans="1:8">
       <c r="A54" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B54" s="9">
-        <v>40113</v>
+        <v>40131</v>
       </c>
       <c r="C54" s="9">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:8">
       <c r="A55" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B55" s="9">
-        <v>40114</v>
+        <v>40132</v>
       </c>
       <c r="C55" s="9">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1" spans="1:8">
       <c r="A56" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B56" s="9">
-        <v>40115</v>
+        <v>40133</v>
       </c>
       <c r="C56" s="9">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1" spans="1:8">
       <c r="A57" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B57" s="9">
-        <v>40116</v>
+        <v>40134</v>
       </c>
       <c r="C57" s="9">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1" spans="1:8">
       <c r="A58" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B58" s="9">
-        <v>40117</v>
+        <v>40135</v>
       </c>
       <c r="C58" s="9">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1" spans="1:8">
       <c r="A59" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>145</v>
+        <v>102</v>
+      </c>
+      <c r="B59" s="9">
+        <v>40136</v>
       </c>
       <c r="C59" s="9">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1" spans="1:8">
       <c r="A60" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>150</v>
+        <v>102</v>
+      </c>
+      <c r="B60" s="9">
+        <v>40137</v>
       </c>
       <c r="C60" s="9">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1" spans="1:8">
       <c r="A61" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>153</v>
+        <v>102</v>
+      </c>
+      <c r="B61" s="9">
+        <v>40138</v>
       </c>
       <c r="C61" s="9">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1" spans="1:8">
       <c r="A62" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>156</v>
+        <v>102</v>
+      </c>
+      <c r="B62" s="9">
+        <v>40139</v>
       </c>
       <c r="C62" s="9">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1" spans="1:8">
       <c r="A63" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>160</v>
+        <v>102</v>
+      </c>
+      <c r="B63" s="9">
+        <v>40140</v>
       </c>
       <c r="C63" s="9">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1" spans="1:8">
       <c r="A64" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>163</v>
+        <v>102</v>
+      </c>
+      <c r="B64" s="9">
+        <v>40141</v>
       </c>
       <c r="C64" s="9">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1" spans="1:8">
       <c r="A65" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B65" s="9">
-        <v>40130</v>
+        <v>40142</v>
       </c>
       <c r="C65" s="9">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1" spans="1:8">
       <c r="A66" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B66" s="9">
-        <v>40131</v>
+        <v>40143</v>
       </c>
       <c r="C66" s="9">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1" spans="1:8">
       <c r="A67" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B67" s="9">
-        <v>40132</v>
+        <v>40144</v>
       </c>
       <c r="C67" s="9">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1" spans="1:8">
       <c r="A68" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B68" s="9">
-        <v>40133</v>
+        <v>40145</v>
       </c>
       <c r="C68" s="9">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:8">
       <c r="A69" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B69" s="9">
-        <v>40134</v>
+        <v>40146</v>
       </c>
       <c r="C69" s="9">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1" spans="1:8">
       <c r="A70" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B70" s="9">
-        <v>40135</v>
+        <v>102</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>197</v>
       </c>
       <c r="C70" s="9">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1" spans="1:8">
       <c r="A71" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B71" s="9">
-        <v>40136</v>
+        <v>102</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>200</v>
       </c>
       <c r="C71" s="9">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:8">
       <c r="A72" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B72" s="9">
-        <v>40137</v>
+        <v>102</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>203</v>
       </c>
       <c r="C72" s="9">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73" ht="28" customHeight="1" spans="1:8">
       <c r="A73" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B73" s="9">
-        <v>40138</v>
+        <v>102</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>206</v>
       </c>
       <c r="C73" s="9">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
     </row>
     <row r="74" ht="28" customHeight="1" spans="1:8">
       <c r="A74" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B74" s="9">
-        <v>40139</v>
+        <v>102</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>209</v>
       </c>
       <c r="C74" s="9">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
     </row>
     <row r="75" ht="28" customHeight="1" spans="1:8">
       <c r="A75" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B75" s="9">
-        <v>40140</v>
+        <v>102</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>212</v>
       </c>
       <c r="C75" s="9">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" ht="28" customHeight="1" spans="1:8">
       <c r="A76" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B76" s="9">
-        <v>40141</v>
+        <v>40159</v>
       </c>
       <c r="C76" s="9">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
     </row>
     <row r="77" ht="28" customHeight="1" spans="1:8">
       <c r="A77" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B77" s="9">
-        <v>40142</v>
+        <v>40160</v>
       </c>
       <c r="C77" s="9">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" ht="28" customHeight="1" spans="1:8">
-      <c r="A78" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B78" s="9">
-        <v>40143</v>
-      </c>
-      <c r="C78" s="9">
-        <v>142</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>128</v>
+      <c r="A78" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B78" s="5">
+        <v>40161</v>
+      </c>
+      <c r="C78" s="5">
+        <v>160</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="79" ht="28" customHeight="1" spans="1:8">
-      <c r="A79" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B79" s="9">
-        <v>40144</v>
-      </c>
-      <c r="C79" s="9">
-        <v>143</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>189</v>
+      <c r="A79" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B79" s="5">
+        <v>40162</v>
+      </c>
+      <c r="C79" s="5">
+        <v>161</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="80" ht="28" customHeight="1" spans="1:8">
       <c r="A80" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B80" s="9">
-        <v>40145</v>
+        <v>40163</v>
       </c>
       <c r="C80" s="9">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81" ht="28" customHeight="1" spans="1:8">
       <c r="A81" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B81" s="9">
-        <v>40146</v>
+        <v>40164</v>
       </c>
       <c r="C81" s="9">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="82" ht="28" customHeight="1" spans="1:8">
       <c r="A82" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="C82" s="9">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>147</v>
+        <v>232</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>149</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" ht="28" customHeight="1" spans="1:8">
-      <c r="A83" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C83" s="9">
-        <v>148</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E83" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>149</v>
+      <c r="A83" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B83" s="5">
+        <v>40173</v>
+      </c>
+      <c r="C83" s="5">
+        <v>172</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="84" ht="28" customHeight="1" spans="1:8">
-      <c r="A84" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C84" s="9">
-        <v>150</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>149</v>
+      <c r="A84" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84" s="7">
+        <v>40174</v>
+      </c>
+      <c r="C84" s="7">
+        <v>173</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="85" ht="28" customHeight="1" spans="1:8">
-      <c r="A85" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B85" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="C85" s="9">
-        <v>152</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>159</v>
+      <c r="A85" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B85" s="7">
+        <v>40175</v>
+      </c>
+      <c r="C85" s="7">
+        <v>174</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="86" ht="28" customHeight="1" spans="1:8">
-      <c r="A86" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="C86" s="9">
-        <v>154</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="E86" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>159</v>
+      <c r="A86" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B86" s="7">
+        <v>40176</v>
+      </c>
+      <c r="C86" s="7">
+        <v>175</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="87" ht="28" customHeight="1" spans="1:8">
-      <c r="A87" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C87" s="9">
-        <v>156</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="E87" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>159</v>
+      <c r="A87" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B87" s="7">
+        <v>40177</v>
+      </c>
+      <c r="C87" s="7">
+        <v>176</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="88" ht="28" customHeight="1" spans="1:8">
-      <c r="A88" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B88" s="9">
-        <v>40159</v>
-      </c>
-      <c r="C88" s="9">
-        <v>158</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="E88" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>141</v>
+      <c r="A88" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B88" s="7">
+        <v>40178</v>
+      </c>
+      <c r="C88" s="7">
+        <v>177</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1" spans="1:8">
-      <c r="A89" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89" s="9">
-        <v>40160</v>
-      </c>
-      <c r="C89" s="9">
-        <v>159</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>231</v>
+      <c r="A89" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B89" s="7">
+        <v>40179</v>
+      </c>
+      <c r="C89" s="7">
+        <v>178</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="90" ht="28" customHeight="1" spans="1:8">
-      <c r="A90" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B90" s="5">
-        <v>40161</v>
-      </c>
-      <c r="C90" s="5">
-        <v>160</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>234</v>
+      <c r="A90" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B90" s="7">
+        <v>40180</v>
+      </c>
+      <c r="C90" s="7">
+        <v>179</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="91" ht="28" customHeight="1" spans="1:8">
-      <c r="A91" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B91" s="5">
-        <v>40162</v>
-      </c>
-      <c r="C91" s="5">
-        <v>161</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>128</v>
+      <c r="A91" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B91" s="7">
+        <v>40181</v>
+      </c>
+      <c r="C91" s="7">
+        <v>180</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="92" ht="28" customHeight="1" spans="1:8">
-      <c r="A92" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B92" s="9">
-        <v>40163</v>
-      </c>
-      <c r="C92" s="9">
-        <v>162</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="E92" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H92" s="10" t="s">
-        <v>141</v>
+      <c r="A92" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92" s="7">
+        <v>40182</v>
+      </c>
+      <c r="C92" s="7">
+        <v>181</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="93" ht="28" customHeight="1" spans="1:8">
-      <c r="A93" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B93" s="9">
-        <v>40164</v>
-      </c>
-      <c r="C93" s="9">
-        <v>163</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="E93" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>241</v>
+      <c r="A93" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B93" s="7">
+        <v>40183</v>
+      </c>
+      <c r="C93" s="7">
+        <v>182</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="94" ht="28" customHeight="1" spans="1:8">
-      <c r="A94" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="C94" s="9">
-        <v>164</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E94" s="9" t="s">
+      <c r="A94" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="7">
+        <v>40184</v>
+      </c>
+      <c r="C94" s="7">
+        <v>183</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G94" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="F94" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G94" s="10" t="s">
+      <c r="H94" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="H94" s="10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="95" ht="28" customHeight="1" spans="1:8">
-      <c r="A95" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B95" s="5">
-        <v>40173</v>
-      </c>
-      <c r="C95" s="5">
-        <v>172</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="H95" s="11" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="96" ht="28" customHeight="1" spans="1:8">
-      <c r="A96" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B96" s="7">
-        <v>40174</v>
-      </c>
-      <c r="C96" s="7">
-        <v>173</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="H96" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="97" ht="28" customHeight="1" spans="1:8">
-      <c r="A97" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B97" s="7">
-        <v>40175</v>
-      </c>
-      <c r="C97" s="7">
-        <v>174</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H97" s="8" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="98" ht="28" customHeight="1" spans="1:8">
-      <c r="A98" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B98" s="7">
-        <v>40176</v>
-      </c>
-      <c r="C98" s="7">
-        <v>175</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H98" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="99" ht="28" customHeight="1" spans="1:8">
-      <c r="A99" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B99" s="7">
-        <v>40177</v>
-      </c>
-      <c r="C99" s="7">
-        <v>176</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H99" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="100" ht="28" customHeight="1" spans="1:8">
-      <c r="A100" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B100" s="7">
-        <v>40178</v>
-      </c>
-      <c r="C100" s="7">
-        <v>177</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H100" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="101" ht="28" customHeight="1" spans="1:8">
-      <c r="A101" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B101" s="7">
-        <v>40179</v>
-      </c>
-      <c r="C101" s="7">
-        <v>178</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G101" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H101" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="102" ht="28" customHeight="1" spans="1:8">
-      <c r="A102" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B102" s="7">
-        <v>40180</v>
-      </c>
-      <c r="C102" s="7">
-        <v>179</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G102" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H102" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" ht="28" customHeight="1" spans="1:8">
-      <c r="A103" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B103" s="7">
-        <v>40181</v>
-      </c>
-      <c r="C103" s="7">
-        <v>180</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G103" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H103" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="104" ht="28" customHeight="1" spans="1:8">
-      <c r="A104" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B104" s="7">
-        <v>40182</v>
-      </c>
-      <c r="C104" s="7">
-        <v>181</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G104" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H104" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="105" ht="28" customHeight="1" spans="1:8">
-      <c r="A105" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B105" s="7">
-        <v>40183</v>
-      </c>
-      <c r="C105" s="7">
-        <v>182</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G105" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H105" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="106" ht="28" customHeight="1" spans="1:8">
-      <c r="A106" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B106" s="7">
-        <v>40184</v>
-      </c>
-      <c r="C106" s="7">
-        <v>183</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="E106" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G106" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H106" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
+    </row>
+    <row r="95" ht="28" customHeight="1"/>
+    <row r="96" ht="28" customHeight="1"/>
+    <row r="97" ht="28" customHeight="1"/>
+    <row r="98" ht="28" customHeight="1"/>
+    <row r="99" ht="28" customHeight="1"/>
+    <row r="100" ht="28" customHeight="1"/>
+    <row r="101" ht="28" customHeight="1"/>
+    <row r="102" ht="28" customHeight="1"/>
+    <row r="103" ht="28" customHeight="1"/>
+    <row r="104" ht="28" customHeight="1"/>
+    <row r="105" ht="28" customHeight="1"/>
+    <row r="106" ht="28" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
